--- a/backend/data/financials_by_company/0M5.F.xlsx
+++ b/backend/data/financials_by_company/0M5.F.xlsx
@@ -4611,10 +4611,8 @@
           <t>CA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>95002</t>
-        </is>
+      <c r="E2" t="n">
+        <v>95002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4738,7 +4736,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AM2" t="n">
